--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:52</t>
+    <t xml:space="preserve">2026-09-09 20:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:16</t>
+    <t xml:space="preserve">2026-09-18 17:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
@@ -30,105 +30,105 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talcahuano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepción</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Concepción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talcahuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:07</t>
+    <t xml:space="preserve">2026-09-27 21:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,13 +558,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>139411</v>
+        <v>13395</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>153516</v>
+        <v>10574</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>90.81</v>
+        <v>126.68</v>
       </c>
     </row>
     <row r="3">
@@ -572,13 +572,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>226373</v>
+        <v>4986</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>239776</v>
+        <v>4186</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>94.41</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="4">
@@ -586,13 +586,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>150014</v>
+        <v>17644</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>158167</v>
+        <v>14890</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.85</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="5">
@@ -600,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>124903</v>
+        <v>7980</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>128941</v>
+        <v>6804</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>96.87</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="6">
@@ -614,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>90864</v>
+        <v>17846</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>91963</v>
+        <v>15428</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>98.8</v>
+        <v>115.67</v>
       </c>
     </row>
     <row r="7">
@@ -628,13 +628,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>97306</v>
+        <v>7168</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>98055</v>
+        <v>6355</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.24</v>
+        <v>112.79</v>
       </c>
     </row>
     <row r="8">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>27156</v>
+        <v>13351</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>27152</v>
+        <v>11873</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.01</v>
+        <v>112.45</v>
       </c>
     </row>
     <row r="9">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>28191</v>
+        <v>3976</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>28028</v>
+        <v>3553</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>100.58</v>
+        <v>111.91</v>
       </c>
     </row>
     <row r="10">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>225684</v>
+        <v>25611</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>223751</v>
+        <v>22953</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>100.86</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="11">
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>37770</v>
+        <v>4820</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>37443</v>
+        <v>4325</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>100.87</v>
+        <v>111.45</v>
       </c>
     </row>
     <row r="12">
@@ -698,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>51030</v>
+        <v>24719</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50189</v>
+        <v>22210</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>101.68</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>39609</v>
+        <v>16180</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>38941</v>
+        <v>14671</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>101.72</v>
+        <v>110.29</v>
       </c>
     </row>
     <row r="14">
@@ -726,13 +726,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>60509</v>
+        <v>26185</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>59150</v>
+        <v>23921</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>102.3</v>
+        <v>109.46</v>
       </c>
     </row>
     <row r="15">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>47059</v>
+        <v>33700</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45407</v>
+        <v>31102</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>103.64</v>
+        <v>108.35</v>
       </c>
     </row>
     <row r="16">
@@ -754,13 +754,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>32780</v>
+        <v>28458</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>31122</v>
+        <v>26746</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>105.33</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="17">
@@ -768,13 +768,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11704</v>
+        <v>10559</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>11105</v>
+        <v>9986</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>105.39</v>
+        <v>105.74</v>
       </c>
     </row>
     <row r="18">
@@ -796,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>10559</v>
+        <v>11704</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9986</v>
+        <v>11105</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>105.74</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="20">
@@ -810,13 +810,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>28458</v>
+        <v>32780</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>26746</v>
+        <v>31122</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>106.4</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="21">
@@ -824,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>33700</v>
+        <v>47059</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>31102</v>
+        <v>45407</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>108.35</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="22">
@@ -838,13 +838,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>26185</v>
+        <v>60509</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>23921</v>
+        <v>59150</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>109.46</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="23">
@@ -852,13 +852,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>16180</v>
+        <v>39609</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14671</v>
+        <v>38941</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>110.29</v>
+        <v>101.72</v>
       </c>
     </row>
     <row r="24">
@@ -866,13 +866,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>24719</v>
+        <v>51030</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22210</v>
+        <v>50189</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>111.3</v>
+        <v>101.68</v>
       </c>
     </row>
     <row r="25">
@@ -880,13 +880,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4820</v>
+        <v>37770</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4325</v>
+        <v>37443</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>111.45</v>
+        <v>100.87</v>
       </c>
     </row>
     <row r="26">
@@ -894,13 +894,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>25611</v>
+        <v>225684</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22953</v>
+        <v>223751</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>111.58</v>
+        <v>100.86</v>
       </c>
     </row>
     <row r="27">
@@ -908,13 +908,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3976</v>
+        <v>28191</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3553</v>
+        <v>28028</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>111.91</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="28">
@@ -922,13 +922,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>13351</v>
+        <v>27156</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>11873</v>
+        <v>27152</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>112.45</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="29">
@@ -936,13 +936,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7168</v>
+        <v>97306</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6355</v>
+        <v>98055</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>112.79</v>
+        <v>99.24</v>
       </c>
     </row>
     <row r="30">
@@ -950,13 +950,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>17846</v>
+        <v>90864</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>15428</v>
+        <v>91963</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>115.67</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="31">
@@ -964,13 +964,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7980</v>
+        <v>124903</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6804</v>
+        <v>128941</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>117.28</v>
+        <v>96.87</v>
       </c>
     </row>
     <row r="32">
@@ -978,13 +978,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>17644</v>
+        <v>150014</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>14890</v>
+        <v>158167</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>118.5</v>
+        <v>94.85</v>
       </c>
     </row>
     <row r="33">
@@ -992,13 +992,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4986</v>
+        <v>226373</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4186</v>
+        <v>239776</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>119.11</v>
+        <v>94.41</v>
       </c>
     </row>
     <row r="34">
@@ -1006,13 +1006,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13395</v>
+        <v>139411</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10574</v>
+        <v>153516</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>126.68</v>
+        <v>90.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Antuco</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Nacimiento</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:54</t>
+    <t xml:space="preserve">2026-10-05 05:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
